--- a/Ladybird Analysis Notebooks/ladybird_sizes_demo.xlsx
+++ b/Ladybird Analysis Notebooks/ladybird_sizes_demo.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ladybird sizes" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="ladybird sizes" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">low</t>
+    <t xml:space="preserve">melanic</t>
   </si>
   <si>
-    <t xml:space="preserve">high</t>
+    <t xml:space="preserve">non-melanic</t>
   </si>
 </sst>
 </file>
@@ -152,24 +152,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -245,13 +249,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B66"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -262,476 +372,286 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>6.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>6</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="0" t="n">
-        <v>5</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="0" t="n">
-        <v>4</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="0" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="B16" s="0" t="n">
-        <v>6</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="0" t="n">
-        <v>5</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="0" t="n">
-        <v>5</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="B19" s="0" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="0" t="n">
-        <v>6</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>6</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <v>5</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>3</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>5</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B32" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="B33" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" s="0" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="B36" s="0" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B37" s="0" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B38" s="0" t="n">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B39" s="0" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="B40" s="0" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B41" s="0" t="n">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" s="0" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="B43" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B44" s="0" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="B45" s="0" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="B46" s="0" t="n">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B47" s="0" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="B48" s="0" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" s="0" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B50" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="n">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4"/>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4"/>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4"/>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4"/>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4"/>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4"/>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4"/>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4"/>
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4"/>
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4"/>
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4"/>
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4"/>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4"/>
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4"/>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4"/>
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4"/>
+      <c r="B49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4"/>
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
